--- a/workspace/framework_paper/edf-local/gradient_edf_local_eval/gradient_edf_local_eval_times.xlsx
+++ b/workspace/framework_paper/edf-local/gradient_edf_local_eval/gradient_edf_local_eval_times.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004436774186324328</v>
+        <v>0.00654482999118045</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007494919961318374</v>
+        <v>0.01580850569531321</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1123024249542505</v>
+        <v>0.6616600349918008</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.005040931794792414</v>
+        <v>0.007260955045931041</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009365566540509462</v>
+        <v>0.01658278334885836</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1882425112742931</v>
+        <v>1.035451195975766</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.005553760016337037</v>
+        <v>0.008058335881214589</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009382054256275297</v>
+        <v>0.01667806915938854</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3685008926782757</v>
+        <v>0.9146542728226632</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.006277354233898223</v>
+        <v>0.008884774171747267</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01005127086304128</v>
+        <v>0.02236485004425049</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4050340062286705</v>
+        <v>1.353683497849852</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.006877496675588191</v>
+        <v>0.01290937319863588</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0121993315871805</v>
+        <v>0.03293123073875904</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4844221117533744</v>
+        <v>1.970774980951101</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.00696799824014306</v>
+        <v>0.01120525745209306</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01518268994055688</v>
+        <v>0.03090339239686728</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8003150757774711</v>
+        <v>3.575208633542061</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008573888386599719</v>
+        <v>0.01362835741601884</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04547359433025121</v>
+        <v>0.3542216209508479</v>
       </c>
       <c r="D8" t="n">
-        <v>1.232616999577731</v>
+        <v>5.047328741550445</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01098268416244537</v>
+        <v>0.01419879584107548</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05649353932589293</v>
+        <v>0.3015299178659916</v>
       </c>
       <c r="D9" t="n">
-        <v>1.50113120963797</v>
+        <v>3.256636835336685</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00886443154886365</v>
+        <v>0.01621115420944989</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05557813871651888</v>
+        <v>0.3168629281409085</v>
       </c>
       <c r="D10" t="n">
-        <v>2.215939767956734</v>
+        <v>5.048222897648811</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01395250188419595</v>
+        <v>0.01741697003133595</v>
       </c>
       <c r="C11" t="n">
-        <v>0.08848234249278902</v>
+        <v>0.7496086653880775</v>
       </c>
       <c r="D11" t="n">
-        <v>4.224970652461052</v>
+        <v>5.52838372707367</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009710192447528243</v>
+        <v>0.01954044834710657</v>
       </c>
       <c r="C12" t="n">
-        <v>0.412966146459803</v>
+        <v>0.9400018329918385</v>
       </c>
       <c r="D12" t="n">
-        <v>25.21890632629395</v>
+        <v>7.994593856334686</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01386420088121667</v>
+        <v>0.0533329856954515</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6617586286831647</v>
+        <v>1.152326506972313</v>
       </c>
       <c r="D13" t="n">
-        <v>7.774098954200745</v>
+        <v>11.50136337041855</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01460287408204749</v>
+        <v>0.05099784320220351</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7520390724949538</v>
+        <v>2.624322736673057</v>
       </c>
       <c r="D14" t="n">
-        <v>9.2970436835289</v>
+        <v>17.72628866434097</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03341091322479769</v>
+        <v>0.06459521498298272</v>
       </c>
       <c r="C15" t="n">
-        <v>1.574850985594094</v>
+        <v>7.845157260969281</v>
       </c>
       <c r="D15" t="n">
-        <v>22.31281812667847</v>
+        <v>22.09530580759048</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01497641820111312</v>
+        <v>0.03542912834789604</v>
       </c>
       <c r="C16" t="n">
-        <v>7.320290086232125</v>
+        <v>5.979210470244288</v>
       </c>
       <c r="D16" t="n">
-        <v>31.45615011692047</v>
+        <v>42.07068272590637</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01528104004450142</v>
+        <v>0.03929830678971484</v>
       </c>
       <c r="C17" t="n">
-        <v>6.355246095694602</v>
+        <v>8.532566506639123</v>
       </c>
       <c r="D17" t="n">
-        <v>60.48866271495819</v>
+        <v>100.621442861557</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0179513033630792</v>
+        <v>0.04488126637064851</v>
       </c>
       <c r="C18" t="n">
-        <v>9.044642110019922</v>
+        <v>18.16720809698105</v>
       </c>
       <c r="D18" t="n">
-        <v>98.35680090427398</v>
+        <v>178.7544429302216</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01757206165697426</v>
+        <v>0.03310846432112157</v>
       </c>
       <c r="C19" t="n">
-        <v>14.58308600641787</v>
+        <v>24.55178956836462</v>
       </c>
       <c r="D19" t="n">
-        <v>147.1220757770538</v>
+        <v>295.771330537796</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01875561323016882</v>
+        <v>0.03229887665249407</v>
       </c>
       <c r="C20" t="n">
-        <v>28.5107893371582</v>
+        <v>43.05792214095592</v>
       </c>
       <c r="D20" t="n">
-        <v>268.1389185333252</v>
+        <v>334.9194095611572</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01843973661307246</v>
+        <v>0.03471593688242137</v>
       </c>
       <c r="C21" t="n">
-        <v>70.0985567739606</v>
+        <v>66.25680912077426</v>
       </c>
       <c r="D21" t="n">
-        <v>429.6673047065735</v>
+        <v>470.648498210907</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/edf-local/gradient_edf_local_eval/gradient_edf_local_eval_times.xlsx
+++ b/workspace/framework_paper/edf-local/gradient_edf_local_eval/gradient_edf_local_eval_times.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00654482999118045</v>
+        <v>0.004564100014977157</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01580850569531321</v>
+        <v>0.007609884152188897</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6616600349918008</v>
+        <v>0.1115532325953245</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.007260955045931041</v>
+        <v>0.005662849994841963</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01658278334885836</v>
+        <v>0.01002910828217864</v>
       </c>
       <c r="D3" t="n">
-        <v>1.035451195975766</v>
+        <v>0.1842667858023196</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.008058335881214589</v>
+        <v>0.005380057520233095</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01667806915938854</v>
+        <v>0.008796475082635879</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9146542728226632</v>
+        <v>0.3718120485451072</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008884774171747267</v>
+        <v>0.005700645716860891</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02236485004425049</v>
+        <v>0.01061900837346911</v>
       </c>
       <c r="D5" t="n">
-        <v>1.353683497849852</v>
+        <v>0.4049730947148055</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01290937319863588</v>
+        <v>0.00590958240441978</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03293123073875904</v>
+        <v>0.01196313916705549</v>
       </c>
       <c r="D6" t="n">
-        <v>1.970774980951101</v>
+        <v>0.4856099664699286</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01120525745209306</v>
+        <v>0.006926872553303837</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03090339239686728</v>
+        <v>0.01409203078597784</v>
       </c>
       <c r="D7" t="n">
-        <v>3.575208633542061</v>
+        <v>0.7823421575687826</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01362835741601884</v>
+        <v>0.008095090785063803</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3542216209508479</v>
+        <v>0.04298760854639113</v>
       </c>
       <c r="D8" t="n">
-        <v>5.047328741550445</v>
+        <v>1.167409283984453</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01419879584107548</v>
+        <v>0.01023199669085443</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3015299178659916</v>
+        <v>0.05382825850509107</v>
       </c>
       <c r="D9" t="n">
-        <v>3.256636835336685</v>
+        <v>1.419340071603656</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01621115420944989</v>
+        <v>0.009481402565725147</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3168629281409085</v>
+        <v>0.0534741030074656</v>
       </c>
       <c r="D10" t="n">
-        <v>5.048222897648811</v>
+        <v>2.162894612737</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01741697003133595</v>
+        <v>0.0139598633069545</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7496086653880775</v>
+        <v>0.08714277134276927</v>
       </c>
       <c r="D11" t="n">
-        <v>5.52838372707367</v>
+        <v>4.187140171527862</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01954044834710657</v>
+        <v>0.01019364749081433</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9400018329918385</v>
+        <v>0.415027783010155</v>
       </c>
       <c r="D12" t="n">
-        <v>7.994593856334686</v>
+        <v>25.22202500224114</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0533329856954515</v>
+        <v>0.01405246915062889</v>
       </c>
       <c r="C13" t="n">
-        <v>1.152326506972313</v>
+        <v>0.6616109067760408</v>
       </c>
       <c r="D13" t="n">
-        <v>11.50136337041855</v>
+        <v>7.795535500049591</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.05099784320220351</v>
+        <v>0.01511482235859148</v>
       </c>
       <c r="C14" t="n">
-        <v>2.624322736673057</v>
+        <v>0.7584462932869792</v>
       </c>
       <c r="D14" t="n">
-        <v>17.72628866434097</v>
+        <v>9.326622211933136</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.06459521498298272</v>
+        <v>0.03379857246298343</v>
       </c>
       <c r="C15" t="n">
-        <v>7.845157260969281</v>
+        <v>1.579662116300315</v>
       </c>
       <c r="D15" t="n">
-        <v>22.09530580759048</v>
+        <v>22.39660620689392</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.03542912834789604</v>
+        <v>0.01499602171475999</v>
       </c>
       <c r="C16" t="n">
-        <v>5.979210470244288</v>
+        <v>7.356594855561853</v>
       </c>
       <c r="D16" t="n">
-        <v>42.07068272590637</v>
+        <v>31.50829738855362</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.03929830678971484</v>
+        <v>0.01533327238634229</v>
       </c>
       <c r="C17" t="n">
-        <v>8.532566506639123</v>
+        <v>6.322568330951035</v>
       </c>
       <c r="D17" t="n">
-        <v>100.621442861557</v>
+        <v>60.48416517734528</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.04488126637064851</v>
+        <v>0.01833906580228358</v>
       </c>
       <c r="C18" t="n">
-        <v>18.16720809698105</v>
+        <v>9.040624833926559</v>
       </c>
       <c r="D18" t="n">
-        <v>178.7544429302216</v>
+        <v>98.33775707244872</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.03310846432112157</v>
+        <v>0.01820713686058298</v>
       </c>
       <c r="C19" t="n">
-        <v>24.55178956836462</v>
+        <v>14.59000853270292</v>
       </c>
       <c r="D19" t="n">
-        <v>295.771330537796</v>
+        <v>146.8336452484131</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.03229887665249407</v>
+        <v>0.01969259247416631</v>
       </c>
       <c r="C20" t="n">
-        <v>43.05792214095592</v>
+        <v>28.32005902245641</v>
       </c>
       <c r="D20" t="n">
-        <v>334.9194095611572</v>
+        <v>267.2253146743774</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.03471593688242137</v>
+        <v>0.01842984000686556</v>
       </c>
       <c r="C21" t="n">
-        <v>66.25680912077426</v>
+        <v>70.02919269919396</v>
       </c>
       <c r="D21" t="n">
-        <v>470.648498210907</v>
+        <v>428.8626842880249</v>
       </c>
     </row>
   </sheetData>
